--- a/SGC-CKN/Excel/b56c72d4-4e28-4b03-8dda-28fba34c4819_Hạng_mục_LÔ_CT-02_P11_108_D800_09-04-2026.xlsx
+++ b/SGC-CKN/Excel/b56c72d4-4e28-4b03-8dda-28fba34c4819_Hạng_mục_LÔ_CT-02_P11_108_D800_09-04-2026.xlsx
@@ -1260,16 +1260,16 @@
         <v>-18.2</v>
       </c>
       <c r="G14" s="16">
-        <v>-26.1</v>
+        <v>-28.1</v>
       </c>
       <c r="H14" s="16">
         <v>1</v>
       </c>
       <c r="I14" s="16">
-        <v>7.9</v>
+        <v>9.9</v>
       </c>
       <c r="J14" s="8">
-        <v>7.9</v>
+        <v>9.9</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>34</v>
@@ -1292,19 +1292,19 @@
         <v>43</v>
       </c>
       <c r="F15" s="19">
-        <v>-26.1</v>
+        <v>-28.1</v>
       </c>
       <c r="G15" s="19">
-        <v>-35.9</v>
+        <v>-35.4</v>
       </c>
       <c r="H15" s="19">
         <v>0.5</v>
       </c>
       <c r="I15" s="19">
-        <v>9.8</v>
+        <v>7.3</v>
       </c>
       <c r="J15" s="8">
-        <v>19.6</v>
+        <v>14.6</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>34</v>
@@ -1327,7 +1327,7 @@
         <v>46</v>
       </c>
       <c r="F16" s="22">
-        <v>-35.9</v>
+        <v>-35.4</v>
       </c>
       <c r="G16" s="22">
         <v>-38.2</v>
@@ -1336,10 +1336,10 @@
         <v>0.5</v>
       </c>
       <c r="I16" s="22">
-        <v>2.3</v>
-      </c>
-      <c r="J16" s="15">
-        <v>4.6</v>
+        <v>2.8</v>
+      </c>
+      <c r="J16" s="8">
+        <v>5.6</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>34</v>
@@ -1654,16 +1654,16 @@
         <v>-18.2</v>
       </c>
       <c r="F5" s="16">
-        <v>-26.1</v>
+        <v>-28.1</v>
       </c>
       <c r="G5" s="16">
         <v>1</v>
       </c>
       <c r="H5" s="16">
-        <v>7.9</v>
+        <v>9.9</v>
       </c>
       <c r="I5" s="8">
-        <v>7.9</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1680,19 +1680,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="19">
-        <v>-26.1</v>
+        <v>-28.1</v>
       </c>
       <c r="F6" s="19">
-        <v>-35.9</v>
+        <v>-35.4</v>
       </c>
       <c r="G6" s="19">
         <v>0.5</v>
       </c>
       <c r="H6" s="19">
-        <v>9.8</v>
+        <v>7.3</v>
       </c>
       <c r="I6" s="8">
-        <v>19.6</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1709,7 +1709,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>-35.9</v>
+        <v>-35.4</v>
       </c>
       <c r="F7" s="22">
         <v>-38.2</v>
@@ -1718,10 +1718,10 @@
         <v>0.5</v>
       </c>
       <c r="H7" s="22">
-        <v>2.3</v>
-      </c>
-      <c r="I7" s="15">
-        <v>4.6</v>
+        <v>2.8</v>
+      </c>
+      <c r="I7" s="8">
+        <v>5.6</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
